--- a/out/Attention_Base_repeat_4_000001.xlsx
+++ b/out/Attention_Base_repeat_4_000001.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,17 +35122,17 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC43" t="n">
-        <v>0</v>
+        <v>-3.997815127472859e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,21 +35913,21 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0</v>
+        <v>0.01721343121673911</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>0.03447280053031293</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.06650458816949664</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC45" t="n">
-        <v>-7.482534500304609e-06</v>
+        <v>0.1503125648032662</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.003687930915888069</v>
+        <v>0.02045718412648821</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.003695413450388354</v>
+        <v>0.1246381556901587</v>
       </c>
     </row>
     <row r="47">
@@ -38298,21 +38298,21 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0</v>
+        <v>0.004148456709721048</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.003702214558871463</v>
+        <v>0.1124485470426455</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.001483529849924623</v>
+        <v>0.00359188650882811</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.278093362574747</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.0007229566599139944</v>
+        <v>0.1154797786514673</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.0006999508940314185</v>
+        <v>0.001753444531976468</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.278093362574747</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.0008102310548472451</v>
+        <v>0.1153910713691376</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0003080345787352447</v>
+        <v>0.0008342235435506434</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.278093362574747</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.0008956815830830019</v>
+        <v>0.1153042190055349</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>8.274560059057353e-05</v>
+        <v>0.0003446140075095411</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.278093362574747</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.001039283180805971</v>
+        <v>0.1151582599755391</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0001053669446193266</v>
+        <v>0.0002373048478682023</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.278093362574747</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.0009117486224906752</v>
+        <v>0.1152879391059952</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>3.038767720092586e-05</v>
+        <v>9.61530627153065e-05</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.1348825055873002</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.0009563689441673924</v>
+        <v>0.1152426769818787</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>1.453295183356064e-05</v>
+        <v>4.711738566636162e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.0009577702101612231</v>
+        <v>0.1152413221421279</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>-6.9568019527284e-07</v>
+        <v>1.546969937155907e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.278093362574747</v>
+        <v>4.206964148813839</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.0009740095245554112</v>
+        <v>0.1152249393480336</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>-1.99540936204904e-06</v>
+        <v>6.452665226717778e-06</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.278093362574747</v>
+        <v>4.206964148813839</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.0009771687137087575</v>
+        <v>0.115221826699907</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>-3.498251797817692e-06</v>
+        <v>6.467173218827975e-07</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.278093362574747</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.0009823408953433391</v>
+        <v>0.1152166545182723</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>-4.408356481861036e-06</v>
+        <v>-2.335871922010791e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.278093362574747</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.0009876659276883584</v>
+        <v>0.1152113294859275</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-4.766625293503456e-06</v>
+        <v>-4.077656293461284e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.278093362574747</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1152059684834257</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>-4.586597321616299e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.278093362574747</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC60" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.115200823909492</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0</v>
+        <v>-4.68213567138761e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC61" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.115195631623775</v>
       </c>
     </row>
     <row r="62">
@@ -50227,17 +50227,17 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC62" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151954961151693</v>
       </c>
     </row>
     <row r="63">
@@ -51022,17 +51022,17 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC63" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151955359706415</v>
       </c>
     </row>
     <row r="64">
@@ -51817,17 +51817,17 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC64" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151955758261138</v>
       </c>
     </row>
     <row r="65">
@@ -52612,17 +52612,17 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC65" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151955678550194</v>
       </c>
     </row>
     <row r="66">
@@ -53407,17 +53407,17 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC66" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151957272769085</v>
       </c>
     </row>
     <row r="67">
@@ -54202,17 +54202,17 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC67" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.115195631623775</v>
       </c>
     </row>
     <row r="68">
@@ -54997,17 +54997,17 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC68" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151959823519313</v>
       </c>
     </row>
     <row r="69">
@@ -55792,17 +55792,17 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC69" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151957352480029</v>
       </c>
     </row>
     <row r="70">
@@ -56587,17 +56587,17 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC70" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151956953925306</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC71" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.115195631623775</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC72" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151957033636251</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC73" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.115195631623775</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC74" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151957352480029</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC75" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151958309011366</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC76" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151957671323807</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC77" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151957272769085</v>
       </c>
     </row>
     <row r="78">
@@ -62947,17 +62947,17 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC78" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151957033636251</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC79" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.115195456259697</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC80" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151953765487522</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC81" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151954243753189</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC82" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.115195543941736</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC83" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151955279995471</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC84" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.115195543941736</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC85" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151955279995471</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC86" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151955837972083</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC87" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151955837972083</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC88" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151955837972083</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC89" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151957352480029</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC90" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151959504675535</v>
       </c>
     </row>
     <row r="91">
@@ -73282,17 +73282,17 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC91" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151958627855144</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC92" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151958149589477</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC93" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151958627855144</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC94" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151956794503417</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC95" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151956874214362</v>
       </c>
     </row>
     <row r="96">
@@ -77257,17 +77257,17 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC96" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151956953925306</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC97" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151957033636251</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC98" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151957033636251</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC99" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151957432190974</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA100" t="n">
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC100" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151958069878533</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC101" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151959185831756</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC102" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151959664097424</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC103" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151959265542701</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA104" t="n">
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC104" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.11519585481442</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA105" t="n">
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC105" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151959743808368</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC106" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151958149589477</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC107" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151955837972083</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC108" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151955359706415</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC109" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151955678550194</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC110" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.115195631623775</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC111" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.115195631623775</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC112" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151955519128304</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC113" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151954323464134</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC114" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151953924909411</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC115" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151955359706415</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC116" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151956714792473</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC117" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151956555370584</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC118" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.115195631623775</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA119" t="n">
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC119" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151955917683027</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC120" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151954881440748</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC121" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151953685776577</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC122" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151954881440748</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC123" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151955359706415</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC124" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.115195631623775</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC125" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151955120573582</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0</v>
+        <v>-4.79359707945414e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell (Force)</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC126" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1151955200284526</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention_Base_repeat_4_000001.xlsx
+++ b/out/Attention_Base_repeat_4_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.703898596494605</v>
+        <v>1.334101894739158</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.703898596494605</v>
+        <v>0.6525037326661627</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.02909442940683214</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,17 +35917,17 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>-4.17584889571881e-05</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.0843581945988276</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC45" t="n">
-        <v>-7.482534500304609e-06</v>
+        <v>0.16886553215571</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.003687930915888069</v>
+        <v>0.02352296128755164</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.003695413450388354</v>
+        <v>0.1314290623162889</v>
       </c>
     </row>
     <row r="47">
@@ -38298,21 +38298,21 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0</v>
+        <v>0.002898382824287518</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.003702214558871463</v>
+        <v>0.1136573928453985</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.001483529849924623</v>
+        <v>0.003662783050380819</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.0007229566599139944</v>
+        <v>0.118079526267414</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.0006999508940314185</v>
+        <v>0.0017708157232728</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.0008102310548472451</v>
+        <v>0.1179524642550042</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0003080345787352447</v>
+        <v>0.0008243552230706816</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.0008956815830830019</v>
+        <v>0.1178281077864254</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>8.274560059057353e-05</v>
+        <v>0.0003078054377767303</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.001039283180805971</v>
+        <v>0.117617505124839</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0001053669446193266</v>
+        <v>0.0002498549883277019</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.0009117486224906752</v>
+        <v>0.1178089479329567</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>3.038767720092586e-05</v>
+        <v>9.325645136701034e-05</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.0009563689441673924</v>
+        <v>0.1177452216500095</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>1.453295183356064e-05</v>
+        <v>4.663653491537832e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.0009577702101612231</v>
+        <v>0.1177455381550123</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>-6.9568019527284e-07</v>
+        <v>1.2649738552242e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.0009740095245554112</v>
+        <v>0.1177239679850435</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>-1.99540936204904e-06</v>
+        <v>5.364997615807159e-06</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.0009771687137087575</v>
+        <v>0.1177217046452602</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>-3.498251797817692e-06</v>
+        <v>-1.076694556079003e-07</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.0009823408953433391</v>
+        <v>0.1177164556198772</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>-4.408356481861036e-06</v>
+        <v>-2.776757543937016e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.0009876659276883584</v>
+        <v>0.1177109686902165</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-4.766625293503456e-06</v>
+        <v>-4.016190788706517e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1177053901649136</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>-4.603633744124571e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC60" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1177001966701795</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0</v>
+        <v>-4.897355221833597e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC61" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1176950043844625</v>
       </c>
     </row>
     <row r="62">
@@ -50227,17 +50227,17 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC62" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1176512060818311</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>0.0003100437062433586</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC63" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1227522382665309</v>
       </c>
     </row>
     <row r="64">
@@ -51813,21 +51813,21 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0</v>
+        <v>0.004722376105345802</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC64" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.12747466916533</v>
       </c>
     </row>
     <row r="65">
@@ -52608,21 +52608,21 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0</v>
+        <v>0.002122000042928172</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC65" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.126961648068005</v>
       </c>
     </row>
     <row r="66">
@@ -53403,21 +53403,21 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0</v>
+        <v>0.003451990607378525</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC66" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1317313121508425</v>
       </c>
     </row>
     <row r="67">
@@ -54198,21 +54198,21 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0</v>
+        <v>0.001005715681857401</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC67" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1302815739067204</v>
       </c>
     </row>
     <row r="68">
@@ -54993,21 +54993,21 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0</v>
+        <v>0.001816529565715439</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC68" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1329066842572095</v>
       </c>
     </row>
     <row r="69">
@@ -55788,21 +55788,21 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0</v>
+        <v>0.000442018060847217</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC69" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1319712418642908</v>
       </c>
     </row>
     <row r="70">
@@ -56583,21 +56583,21 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0</v>
+        <v>0.0001811296510755821</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC70" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1318903618738095</v>
       </c>
     </row>
     <row r="71">
@@ -57378,21 +57378,21 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0</v>
+        <v>5.822858651310776e-05</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC71" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1318249589020447</v>
       </c>
     </row>
     <row r="72">
@@ -58173,21 +58173,21 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0</v>
+        <v>4.345292740374758e-05</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC72" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1318534262302679</v>
       </c>
     </row>
     <row r="73">
@@ -58968,21 +58968,21 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>0</v>
+        <v>1.073988217453959e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC73" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1318314527698532</v>
       </c>
     </row>
     <row r="74">
@@ -59763,21 +59763,21 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>0</v>
+        <v>9.043698397223537e-06</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC74" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1318386153046212</v>
       </c>
     </row>
     <row r="75">
@@ -60558,21 +60558,21 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>0</v>
+        <v>4.673446948782985e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC75" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1318392235006026</v>
       </c>
     </row>
     <row r="76">
@@ -61353,21 +61353,21 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>0</v>
+        <v>-9.518764552391623e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC76" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1318322933070296</v>
       </c>
     </row>
     <row r="77">
@@ -62148,21 +62148,21 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>0</v>
+        <v>-3.38952919927794e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC77" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.13182668781531</v>
       </c>
     </row>
     <row r="78">
@@ -62943,21 +62943,21 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>0</v>
+        <v>-4.175269320787275e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC78" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1318214922468925</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC79" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1317846043849653</v>
       </c>
     </row>
     <row r="80">
@@ -64533,21 +64533,21 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>0</v>
+        <v>-0.009025438802057565</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC80" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1227593250057911</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC81" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1227246599730221</v>
       </c>
     </row>
     <row r="82">
@@ -66123,21 +66123,21 @@
         <v>0</v>
       </c>
       <c r="IY82" t="n">
-        <v>0</v>
+        <v>0.006744111256276383</v>
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC82" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1362750895121528</v>
       </c>
     </row>
     <row r="83">
@@ -66918,21 +66918,21 @@
         <v>0</v>
       </c>
       <c r="IY83" t="n">
-        <v>0</v>
+        <v>0.002918930430100133</v>
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC83" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1353371580607495</v>
       </c>
     </row>
     <row r="84">
@@ -67713,21 +67713,21 @@
         <v>0</v>
       </c>
       <c r="IY84" t="n">
-        <v>0</v>
+        <v>0.001684108492351611</v>
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC84" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1357734793972767</v>
       </c>
     </row>
     <row r="85">
@@ -68508,21 +68508,21 @@
         <v>0</v>
       </c>
       <c r="IY85" t="n">
-        <v>0</v>
+        <v>0.0007263051094397898</v>
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC85" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1355355052675849</v>
       </c>
     </row>
     <row r="86">
@@ -69303,21 +69303,21 @@
         <v>0</v>
       </c>
       <c r="IY86" t="n">
-        <v>0</v>
+        <v>0.0005589423996702535</v>
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC86" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1359242807427025</v>
       </c>
     </row>
     <row r="87">
@@ -70098,21 +70098,21 @@
         <v>0</v>
       </c>
       <c r="IY87" t="n">
-        <v>0</v>
+        <v>0.0002769711998351267</v>
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC87" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1359176404016165</v>
       </c>
     </row>
     <row r="88">
@@ -70893,21 +70893,21 @@
         <v>0</v>
       </c>
       <c r="IY88" t="n">
-        <v>0</v>
+        <v>0.0001359063500019267</v>
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC88" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1359118206921027</v>
       </c>
     </row>
     <row r="89">
@@ -71688,21 +71688,21 @@
         <v>0</v>
       </c>
       <c r="IY89" t="n">
-        <v>0</v>
+        <v>0.0001328471538596374</v>
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC89" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.136041120708927</v>
       </c>
     </row>
     <row r="90">
@@ -72483,21 +72483,21 @@
         <v>0</v>
       </c>
       <c r="IY90" t="n">
-        <v>0</v>
+        <v>0.00011149009819805</v>
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC90" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1361315910310315</v>
       </c>
     </row>
     <row r="91">
@@ -73278,21 +73278,21 @@
         <v>0</v>
       </c>
       <c r="IY91" t="n">
-        <v>0</v>
+        <v>4.352402200979391e-05</v>
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC91" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1361068984266445</v>
       </c>
     </row>
     <row r="92">
@@ -74073,21 +74073,21 @@
         <v>0</v>
       </c>
       <c r="IY92" t="n">
-        <v>0</v>
+        <v>1.680551388702005e-05</v>
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC92" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1360964746818526</v>
       </c>
     </row>
     <row r="93">
@@ -74868,21 +74868,21 @@
         <v>0</v>
       </c>
       <c r="IY93" t="n">
-        <v>0</v>
+        <v>7.240293840308374e-06</v>
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC93" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.136094117777962</v>
       </c>
     </row>
     <row r="94">
@@ -75663,21 +75663,21 @@
         <v>0</v>
       </c>
       <c r="IY94" t="n">
-        <v>0</v>
+        <v>-1.443465465376004e-06</v>
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC94" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1360839698773453</v>
       </c>
     </row>
     <row r="95">
@@ -76458,21 +76458,21 @@
         <v>0</v>
       </c>
       <c r="IY95" t="n">
-        <v>0</v>
+        <v>-3.166002028654738e-06</v>
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC95" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1360790741478186</v>
       </c>
     </row>
     <row r="96">
@@ -77253,21 +77253,21 @@
         <v>0</v>
       </c>
       <c r="IY96" t="n">
-        <v>0</v>
+        <v>-4.190116281980631e-06</v>
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC96" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.136074126777563</v>
       </c>
     </row>
     <row r="97">
@@ -78048,21 +78048,21 @@
         <v>0</v>
       </c>
       <c r="IY97" t="n">
-        <v>0</v>
+        <v>-4.444154463025202e-06</v>
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC97" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1360691565308655</v>
       </c>
     </row>
     <row r="98">
@@ -78843,21 +78843,21 @@
         <v>0</v>
       </c>
       <c r="IY98" t="n">
-        <v>0</v>
+        <v>-4.722077231512602e-06</v>
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC98" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1360641554653279</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC99" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1360641953208002</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA100" t="n">
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC100" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.136064259089556</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC101" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1360643706848784</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC102" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1360644185114452</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC103" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1360643786559729</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA104" t="n">
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC104" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1360643069161228</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA105" t="n">
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC105" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1360644264825396</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC106" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1360642670606505</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC107" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1360640358989111</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC108" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1360639880723443</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC109" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1360640199567222</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC110" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1360640837254778</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC111" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1360640837254778</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC112" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1360640040145333</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC113" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1360425611594808</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC114" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1332820655117284</v>
       </c>
     </row>
     <row r="115">
@@ -92358,21 +92358,21 @@
         <v>0</v>
       </c>
       <c r="IY115" t="n">
-        <v>0</v>
+        <v>0.003770443306435856</v>
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC115" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1436171475025094</v>
       </c>
     </row>
     <row r="116">
@@ -93153,21 +93153,21 @@
         <v>0</v>
       </c>
       <c r="IY116" t="n">
-        <v>0</v>
+        <v>0.004330643293996767</v>
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC116" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.148492485572628</v>
       </c>
     </row>
     <row r="117">
@@ -93948,21 +93948,21 @@
         <v>0</v>
       </c>
       <c r="IY117" t="n">
-        <v>0</v>
+        <v>0.002018909046126188</v>
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC117" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1481902029442405</v>
       </c>
     </row>
     <row r="118">
@@ -94743,21 +94743,21 @@
         <v>0</v>
       </c>
       <c r="IY118" t="n">
-        <v>0</v>
+        <v>0.0008990200724089568</v>
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC118" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1479646485552618</v>
       </c>
     </row>
     <row r="119">
@@ -95538,21 +95538,21 @@
         <v>0</v>
       </c>
       <c r="IY119" t="n">
-        <v>0</v>
+        <v>0.0003569845401325496</v>
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA119" t="n">
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC119" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1477774371389735</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC120" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1475250709417825</v>
       </c>
     </row>
     <row r="121">
@@ -97128,21 +97128,21 @@
         <v>0</v>
       </c>
       <c r="IY121" t="n">
-        <v>0</v>
+        <v>-0.006647642333907456</v>
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC121" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1407473691133859</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC122" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1407291704623252</v>
       </c>
     </row>
     <row r="123">
@@ -98718,21 +98718,21 @@
         <v>0</v>
       </c>
       <c r="IY123" t="n">
-        <v>0</v>
+        <v>0.0002082539910782615</v>
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC123" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1433078525820156</v>
       </c>
     </row>
     <row r="124">
@@ -99513,21 +99513,21 @@
         <v>0</v>
       </c>
       <c r="IY124" t="n">
-        <v>0</v>
+        <v>0.003525230770391969</v>
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC124" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1480183691565637</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC125" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1450467295529416</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0</v>
+        <v>0.0009289279716143612</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell (Force)</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC126" t="n">
-        <v>-0.0009930303850664058</v>
+        <v>0.1454334070818722</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention_Base_repeat_4_000001.xlsx
+++ b/out/Attention_Base_repeat_4_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.009998451918363571</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.3</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.003537623677402735</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.3</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.004635751713067293</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.534101894739158</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.006033343728631735</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.534101894739158</v>
+        <v>-0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.006039886269718409</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.534101894739158</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.003995595034211874</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.534101894739158</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.005170122254639864</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.534101894739158</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.006076572928577662</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.534101894739158</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.006215960253030062</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.534101894739158</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.007203369867056608</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.334101894739158</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.0074646663852036</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.334101894739158</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.008008383214473724</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.334101894739158</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.00783918984234333</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.334101894739158</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.006842632312327623</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.16</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.005484872963279486</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.004194376524537802</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.003778453450649977</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.003386485856026411</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.003101192880421877</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.003309280145913363</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.003503976855427027</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.0034261136315763</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.003071385901421309</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.002591835800558329</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.002457011956721544</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.002436481881886721</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.002473113592714071</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.002739748451858759</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.002772109117358923</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.002175678033381701</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.002211127895861864</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.002084144856780767</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.002272832673043013</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.002512277569621801</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.002819966990500689</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.002987491432577372</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.003051492851227522</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.003048903774470091</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.00262537831440568</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.001882876735180616</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.334101894739158</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.0006792661733925343</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.6525037326661627</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,17 +35122,17 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.0006020991131663322</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.02909442940683214</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>0</v>
+        <v>-1.832464563928079e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,21 +35913,21 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0</v>
+        <v>0.007889953300800185</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.001391374040395021</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>-4.17584889571881e-05</v>
+        <v>0.01580117777179286</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.0843581945988276</v>
+        <v>0.03048388960583396</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.001770894508808851</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.16886553215571</v>
+        <v>0.06889896671024384</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.02352296128755164</v>
+        <v>0.00937620908896813</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.005284918937832117</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1314290623162889</v>
+        <v>0.05712971148819337</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.002898382824287518</v>
+        <v>0.001898719333956945</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.007448046468198299</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1136573928453985</v>
+        <v>0.05153961946045398</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.003662783050380819</v>
+        <v>0.001643811630141548</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.009646568447351456</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.118079526267414</v>
+        <v>0.05292642706298525</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.0017708157232728</v>
+        <v>0.0008007204045799818</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.009668190032243729</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.1179524642550042</v>
+        <v>0.052883056390716</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0008243552230706816</v>
+        <v>0.0003798668479977473</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.01056564692407846</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.1178281077864254</v>
+        <v>0.05284051900103851</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0003078054377767303</v>
+        <v>0.0001553325384757131</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.01119912043213844</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.117617505124839</v>
+        <v>0.05277087536944775</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0002498549883277019</v>
+        <v>0.0001061206945637616</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.01160847395658493</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.1178089479329567</v>
+        <v>0.05282763904710929</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>9.325645136701034e-05</v>
+        <v>4.138866570383483e-05</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.01130022946745157</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.1177452216500095</v>
+        <v>0.05280417488827859</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>4.663653491537832e-05</v>
+        <v>1.905417799985921e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.01205625757575035</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.1177455381550123</v>
+        <v>0.05280084623303218</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>1.2649738552242e-05</v>
+        <v>4.447553556104185e-06</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.01370105985552073</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.1177239679850435</v>
+        <v>0.05279065885715792</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>5.364997615807159e-06</v>
+        <v>1.536993520230006e-07</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.01382650621235371</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.1177217046452602</v>
+        <v>0.05278650816550106</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>-1.076694556079003e-07</v>
+        <v>-2.741313071246881e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.01437239348888397</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.1177164556198772</v>
+        <v>0.05278143132175273</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>-2.776757543937016e-06</v>
+        <v>-3.934348768804317e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.0139587614685297</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.1177109686902165</v>
+        <v>0.05277626942443685</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-4.016190788706517e-06</v>
+        <v>-4.538828146730642e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.0138758048415184</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.1177053901649136</v>
+        <v>0.05277105305326101</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-4.603633744124571e-06</v>
+        <v>-4.586597321616299e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.01373888924717903</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.1177001966701795</v>
+        <v>0.05276595630589383</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.897355221833597e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.01368856988847256</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.1176950043844625</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="62">
@@ -50227,17 +50227,17 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.01395065896213055</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.1176512060818311</v>
+        <v>0.05276572514415463</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0003100437062433586</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.01349270157516003</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.1227522382665309</v>
+        <v>0.0527657649996269</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.004722376105345802</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.01389714330434799</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.12747466916533</v>
+        <v>0.05276580485509918</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.002122000042928172</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.01320058479905128</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.126961648068005</v>
+        <v>0.05276579688400473</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.003451990607378525</v>
+        <v>0</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.01340741850435734</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.1317313121508425</v>
+        <v>0.05276595630589383</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.001005715681857401</v>
+        <v>0</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.01276784390211105</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.1302815739067204</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.001816529565715439</v>
+        <v>0</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.01319891214370728</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.1329066842572095</v>
+        <v>0.05276621138091665</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.000442018060847217</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.01396467164158821</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.1319712418642908</v>
+        <v>0.05276596427698829</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0001811296510755821</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.01382634416222572</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.1318903618738095</v>
+        <v>0.05276592442151602</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>5.822858651310776e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.01437881402671337</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.1318249589020447</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>4.345292740374758e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.01414328441023827</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.1318534262302679</v>
+        <v>0.05276593239261047</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>1.073988217453959e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.01409796066582203</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.1318314527698532</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>9.043698397223537e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.01217100769281387</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.1318386153046212</v>
+        <v>0.05276596427698829</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>4.673446948782985e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.01388290710747242</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.1318392235006026</v>
+        <v>0.05276605993012199</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>-9.518764552391623e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.01507128961384296</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.1318322933070296</v>
+        <v>0.05276599616136612</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-3.38952919927794e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.0153264831751585</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.13182668781531</v>
+        <v>0.05276595630589383</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-4.175269320787275e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.01479404419660568</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.1318214922468925</v>
+        <v>0.05276593239261047</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.01539735309779644</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.1317846043849653</v>
+        <v>0.05276568528868235</v>
       </c>
     </row>
     <row r="80">
@@ -64533,21 +64533,21 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>-0.009025438802057565</v>
+        <v>0</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.01548921316862106</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.1227593250057911</v>
+        <v>0.05276560557773756</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.01508021727204323</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.1227246599730221</v>
+        <v>0.05276565340430429</v>
       </c>
     </row>
     <row r="82">
@@ -66123,7 +66123,7 @@
         <v>0</v>
       </c>
       <c r="IY82" t="n">
-        <v>0.006744111256276383</v>
+        <v>0</v>
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.01486670970916748</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.1362750895121528</v>
+        <v>0.05276577297072136</v>
       </c>
     </row>
     <row r="83">
@@ -66918,7 +66918,7 @@
         <v>0</v>
       </c>
       <c r="IY83" t="n">
-        <v>0.002918930430100133</v>
+        <v>0</v>
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.01433401182293892</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.1353371580607495</v>
+        <v>0.05276575702853245</v>
       </c>
     </row>
     <row r="84">
@@ -67713,7 +67713,7 @@
         <v>0</v>
       </c>
       <c r="IY84" t="n">
-        <v>0.001684108492351611</v>
+        <v>0</v>
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.01420970074832439</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.16</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.1357734793972767</v>
+        <v>0.05276577297072136</v>
       </c>
     </row>
     <row r="85">
@@ -68508,7 +68508,7 @@
         <v>0</v>
       </c>
       <c r="IY85" t="n">
-        <v>0.0007263051094397898</v>
+        <v>0</v>
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.01387338899075985</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.1355355052675849</v>
+        <v>0.05276575702853245</v>
       </c>
     </row>
     <row r="86">
@@ -69303,7 +69303,7 @@
         <v>0</v>
       </c>
       <c r="IY86" t="n">
-        <v>0.0005589423996702535</v>
+        <v>0</v>
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.01376068964600563</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.1359242807427025</v>
+        <v>0.05276581282619364</v>
       </c>
     </row>
     <row r="87">
@@ -70098,7 +70098,7 @@
         <v>0</v>
       </c>
       <c r="IY87" t="n">
-        <v>0.0002769711998351267</v>
+        <v>0</v>
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.01382088474929333</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.1359176404016165</v>
+        <v>0.05276581282619364</v>
       </c>
     </row>
     <row r="88">
@@ -70893,7 +70893,7 @@
         <v>0</v>
       </c>
       <c r="IY88" t="n">
-        <v>0.0001359063500019267</v>
+        <v>0</v>
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.012734679505229</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.1359118206921027</v>
+        <v>0.05276581282619364</v>
       </c>
     </row>
     <row r="89">
@@ -71688,7 +71688,7 @@
         <v>0</v>
       </c>
       <c r="IY89" t="n">
-        <v>0.0001328471538596374</v>
+        <v>0</v>
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.01321320794522762</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.136041120708927</v>
+        <v>0.05276596427698829</v>
       </c>
     </row>
     <row r="90">
@@ -72483,7 +72483,7 @@
         <v>0</v>
       </c>
       <c r="IY90" t="n">
-        <v>0.00011149009819805</v>
+        <v>0</v>
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.01211314089596272</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.1361315910310315</v>
+        <v>0.05276617949653883</v>
       </c>
     </row>
     <row r="91">
@@ -73278,7 +73278,7 @@
         <v>0</v>
       </c>
       <c r="IY91" t="n">
-        <v>4.352402200979391e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.01314528472721577</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.1361068984266445</v>
+        <v>0.05276609181449982</v>
       </c>
     </row>
     <row r="92">
@@ -74073,7 +74073,7 @@
         <v>0</v>
       </c>
       <c r="IY92" t="n">
-        <v>1.680551388702005e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.01293210964649916</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.1360964746818526</v>
+        <v>0.05276604398793308</v>
       </c>
     </row>
     <row r="93">
@@ -74868,7 +74868,7 @@
         <v>0</v>
       </c>
       <c r="IY93" t="n">
-        <v>7.240293840308374e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.01269654743373394</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.136094117777962</v>
+        <v>0.05276609181449982</v>
       </c>
     </row>
     <row r="94">
@@ -75663,7 +75663,7 @@
         <v>0</v>
       </c>
       <c r="IY94" t="n">
-        <v>-1.443465465376004e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.01309622451663017</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.1360839698773453</v>
+        <v>0.05276590847932711</v>
       </c>
     </row>
     <row r="95">
@@ -76458,7 +76458,7 @@
         <v>0</v>
       </c>
       <c r="IY95" t="n">
-        <v>-3.166002028654738e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.01289871335029602</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.1360790741478186</v>
+        <v>0.05276591645042156</v>
       </c>
     </row>
     <row r="96">
@@ -77253,7 +77253,7 @@
         <v>0</v>
       </c>
       <c r="IY96" t="n">
-        <v>-4.190116281980631e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.01246596686542034</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.136074126777563</v>
+        <v>0.05276592442151602</v>
       </c>
     </row>
     <row r="97">
@@ -78048,7 +78048,7 @@
         <v>0</v>
       </c>
       <c r="IY97" t="n">
-        <v>-4.444154463025202e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.01257890276610851</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.1360691565308655</v>
+        <v>0.05276593239261047</v>
       </c>
     </row>
     <row r="98">
@@ -78843,7 +78843,7 @@
         <v>0</v>
       </c>
       <c r="IY98" t="n">
-        <v>-4.722077231512602e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.01229310967028141</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.1360641554653279</v>
+        <v>0.05276593239261047</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.01139285136014223</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.1360641953208002</v>
+        <v>0.05276597224808275</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.01158290263265371</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.136064259089556</v>
+        <v>0.05276603601683862</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.01139792520552874</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.1360643706848784</v>
+        <v>0.052766147612161</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.01173591986298561</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.1360644185114452</v>
+        <v>0.05276619543872774</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.01149933226406574</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.1360643786559729</v>
+        <v>0.05276615558325546</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.01137705519795418</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.1360643069161228</v>
+        <v>0.05276608384340536</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.01136115938425064</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.1360644264825396</v>
+        <v>0.05276620340982219</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.01143050752580166</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.1360642670606505</v>
+        <v>0.05276604398793308</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.01205584034323692</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.16</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.1360640358989111</v>
+        <v>0.05276581282619364</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.01205883547663689</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.3</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.1360639880723443</v>
+        <v>0.0527657649996269</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.01208554953336716</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.3</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.1360640199567222</v>
+        <v>0.05276579688400473</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.01166041567921638</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.16</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.1360640837254778</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.01181275770068169</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.1360640837254778</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.01166935916990042</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.1360640040145333</v>
+        <v>0.05276578094181581</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.01156473904848099</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.1360425611594808</v>
+        <v>0.05276566137539875</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.01140834391117096</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.1332820655117284</v>
+        <v>0.05276562151992647</v>
       </c>
     </row>
     <row r="115">
@@ -92358,7 +92358,7 @@
         <v>0</v>
       </c>
       <c r="IY115" t="n">
-        <v>0.003770443306435856</v>
+        <v>0</v>
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.01098256558179855</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.1436171475025094</v>
+        <v>0.0527657649996269</v>
       </c>
     </row>
     <row r="116">
@@ -93153,7 +93153,7 @@
         <v>0</v>
       </c>
       <c r="IY116" t="n">
-        <v>0.004330643293996767</v>
+        <v>0</v>
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.01088676974177361</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.148492485572628</v>
+        <v>0.05276590050823265</v>
       </c>
     </row>
     <row r="117">
@@ -93948,7 +93948,7 @@
         <v>0</v>
       </c>
       <c r="IY117" t="n">
-        <v>0.002018909046126188</v>
+        <v>0</v>
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.01090473309159279</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.1481902029442405</v>
+        <v>0.05276588456604374</v>
       </c>
     </row>
     <row r="118">
@@ -94743,7 +94743,7 @@
         <v>0</v>
       </c>
       <c r="IY118" t="n">
-        <v>0.0008990200724089568</v>
+        <v>0</v>
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.01065585855394602</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.1479646485552618</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="119">
@@ -95538,7 +95538,7 @@
         <v>0</v>
       </c>
       <c r="IY119" t="n">
-        <v>0.0003569845401325496</v>
+        <v>0</v>
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.01053063105791807</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.1477774371389735</v>
+        <v>0.05276582079728809</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.01030849479138851</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.1475250709417825</v>
+        <v>0.05276571717306017</v>
       </c>
     </row>
     <row r="121">
@@ -97128,21 +97128,21 @@
         <v>0</v>
       </c>
       <c r="IY121" t="n">
-        <v>-0.006647642333907456</v>
+        <v>0</v>
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.01013862621039152</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.1407473691133859</v>
+        <v>0.0527655976066431</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.01044874731451273</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.1407291704623252</v>
+        <v>0.05276571717306017</v>
       </c>
     </row>
     <row r="123">
@@ -98718,21 +98718,21 @@
         <v>0</v>
       </c>
       <c r="IY123" t="n">
-        <v>0.0002082539910782615</v>
+        <v>0</v>
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.01011314801871777</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.1433078525820156</v>
+        <v>0.0527657649996269</v>
       </c>
     </row>
     <row r="124">
@@ -99513,7 +99513,7 @@
         <v>0</v>
       </c>
       <c r="IY124" t="n">
-        <v>0.003525230770391969</v>
+        <v>0</v>
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.01024802774190903</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.1480183691565637</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.01009789761155844</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.3999999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.1450467295529416</v>
+        <v>0.05276574108634353</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0.0009289279716143612</v>
+        <v>-4.79359707945414e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.00973798893392086</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.3999999999999995</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.1454334070818722</v>
+        <v>0.05276574905743799</v>
       </c>
     </row>
   </sheetData>
